--- a/WorkBot/refactor/data/orders/UNFI/UNFI_Triphammer_2025-10-10.xlsx
+++ b/WorkBot/refactor/data/orders/UNFI/UNFI_Triphammer_2025-10-10.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -875,6 +875,33 @@
         </is>
       </c>
     </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>0778936</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Seeds - Pumpkin Seeds Raw</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>32.53</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>32.53</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
